--- a/ConfigExporter/xlsx/runtime_asset.xlsx
+++ b/ConfigExporter/xlsx/runtime_asset.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,6 +578,60 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>chess_board_latest_move_on_black_stone_material</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>黑子最新手三角标记专属不透明材质</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Scenes/Duel/Materials/ChessBoardLatestMoveOnBlackStone</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>chess_board_latest_move_on_white_stone_material</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>白子最新手三角标记专属不透明材质</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Scenes/Duel/Materials/ChessBoardLatestMoveOnWhiteStone</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ConfigExporter/xlsx/runtime_asset.xlsx
+++ b/ConfigExporter/xlsx/runtime_asset.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,7 +510,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>#require#enum(Material,GameObject,Sprite)</t>
+          <t>#require#enum(Material,GameObject,Sprite,AudioClip)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -627,6 +627,182 @@
         </is>
       </c>
       <c r="E8" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>audio_sfx_stone_place_sabaki_00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Audio/SFX/StonePlace/StonePlace_Sabaki_00.mp3</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>audio_sfx_stone_place_sabaki_01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Audio/SFX/StonePlace/StonePlace_Sabaki_01.mp3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>audio_sfx_stone_place_sabaki_02</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Audio/SFX/StonePlace/StonePlace_Sabaki_02.mp3</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>audio_sfx_stone_place_sabaki_03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Audio/SFX/StonePlace/StonePlace_Sabaki_03.mp3</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>audio_sfx_stone_place_sabaki_04</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Audio/SFX/StonePlace/StonePlace_Sabaki_04.mp3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>audio_sfx_capture_single</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Audio/SFX/Capture/Capture_Single.mp3</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>audio_sfx_capture_multi</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Audio/SFX/Capture/Capture_Multi.mp3</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>audio_bgm_happy_moments_piano_full</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Audio/BGM/Active/HappyMomentsPianoFull.ogg</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>runtime_asset</t>
         </is>

--- a/ConfigExporter/xlsx/runtime_asset.xlsx
+++ b/ConfigExporter/xlsx/runtime_asset.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,6 +808,556 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_game_started</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/GameStarted.wav</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_start_counting</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/StartCounting.wav</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_byoyomi</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/Byoyomi.wav</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_overtime</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/Overtime.wav</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_periods_left_5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/PeriodsLeft5.wav</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_periods_left_4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/PeriodsLeft4.wav</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_periods_left_3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/PeriodsLeft3.wav</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_periods_left_2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/PeriodsLeft2.wav</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_last_period</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/LastPeriod.wav</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_countdown_10</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/Countdown10.wav</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_countdown_09</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/Countdown09.wav</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_countdown_08</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/Countdown08.wav</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_countdown_07</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/Countdown07.wav</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_countdown_06</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/Countdown06.wav</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_countdown_05</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/Countdown05.wav</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_countdown_04</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/Countdown04.wav</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_countdown_03</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/Countdown03.wav</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_countdown_02</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/Countdown02.wav</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_countdown_01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/Countdown01.wav</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_remove_dead_stones</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/RemoveDeadStones.wav</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_pass</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/Pass.wav</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_black_wins</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/BlackWins.wav</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_white_wins</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/WhiteWins.wav</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_tie</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/Tie.wav</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>audio_voice_ogs_preview_you_have_won</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AudioClip</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Audio/Voice/OgsPreview/YouHaveWon.wav</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>runtime_asset</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
